--- a/Manuscript_Data/Metallohydrolase_RFdiffusion2_Nature_Methods_2026/raw_wetlab_data/250401_4mu_standard_curves_100uL_30uMladder_and_45uMladder_25C_5prctDMSO__pH8.xlsx
+++ b/Manuscript_Data/Metallohydrolase_RFdiffusion2_Nature_Methods_2026/raw_wetlab_data/250401_4mu_standard_curves_100uL_30uMladder_and_45uMladder_25C_5prctDMSO__pH8.xlsx
@@ -3,11 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20416"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Users\Baker_Lab\woodbuse\neo2_platereader\zinc_hydrolase_ULTRAop\single_zinc_esterase\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{D3296BCE-4084-4173-98FD-E6E6392BADBD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="120" yWindow="120" windowWidth="9435" windowHeight="6915"/>
@@ -35,13 +30,13 @@
     <t>Experiment File Path:</t>
   </si>
   <si>
-    <t>Z:\Users\Baker_Lab\woodbuse\neo2_platereader\zinc_hydrolase_ULTRAop\single_zinc_esterase\250401_4mu_standard_curves_100uL_30uMladder_and_45uMladder_25C_5prctDMSO__pH8.xpt</t>
+    <t>250401_4mu_standard_curves_100uL_30uMladder_and_45uMladder_25C_5prctDMSO__pH8.xpt</t>
   </si>
   <si>
     <t>Protocol File Path:</t>
   </si>
   <si>
-    <t>Z:\Users\Baker_Lab\woodbuse\neo2_platereader\zinc_hydrolase_ULTRAop\single_zinc_esterase\240318_standard_curve.prt</t>
+    <t>240318_standard_curve.prt</t>
   </si>
   <si>
     <t>Plate Number</t>
